--- a/processed_ruby_restored_xlsx/sc239_凛Ｂ：ＥＮＤ.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc239_凛Ｂ：ＥＮＤ.ss.xlsx
@@ -561,8 +561,8 @@
       <c r="B7" s="1" t="inlineStr">
         <is>
           <t>It's endearing how Nono-chan always wants to act like
-the teacher at every little thing, and Miru-chan butts
-in to tease her.</t>
+the teacher at every little thing, and Miru-chan
+butts in to tease her.</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -930,7 +930,8 @@
       <c r="B31" s="1" t="inlineStr">
         <is>
           <t>When the theme was announced, Miru-chan and
-Rurichiyo-chan immediately began to rack their brains.</t>
+Rurichiyo-chan immediately began to rack their
+brains.</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -976,8 +977,8 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>「Anything's fine, okay？ Even your dream for the future
-— so feel free to write whatever you want！」</t>
+          <t>「Anything's fine, okay？ Even your dream for the
+future — so feel free to write whatever you want！」</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1265,8 +1266,8 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>「Alright then, let's finish the chitchat and start the
-essay！」</t>
+          <t>「Alright then, let's finish the chitchat and start
+the essay！」</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1495,9 +1496,9 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>Everyone is diligently, seriously writing their dreams
-for the future, but from where I stand, only Rin-chan
-isn't making any progress with her pen.</t>
+          <t>Everyone is diligently, seriously writing their
+dreams for the future, but from where I stand, only
+Rin-chan isn't making any progress with her pen.</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1926,8 +1927,8 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>You must be taking this composition way too seriously,
-aren't you.</t>
+          <t>You must be taking this composition way too
+seriously, aren't you.</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -2033,8 +2034,8 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>I stood up again and moved in until I was right on the
-edge of Rin-chan’s alert zone.</t>
+          <t>I stood up again and moved in until I was right on
+the edge of Rin-chan’s alert zone.</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2110,7 +2111,8 @@
       <c r="B108" s="1" t="inlineStr">
         <is>
           <t>When I spoke from diagonally behind, Rin-chan glanced
-back at me for a moment, then immediately looked away.</t>
+back at me for a moment, then immediately looked
+away.</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2786,8 +2788,8 @@
       <c r="B152" s="1" t="inlineStr">
         <is>
           <t>「Huh? It’s weird that Rin can’t write an essay—she
-usually scribbles it out quick and then sleeps for the
-rest of the time.」</t>
+usually scribbles it out quick and then sleeps for
+the rest of the time.」</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -3969,9 +3971,9 @@
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t>I'm sure if we actually talked properly I'd think 'oh,
-that's nothing,' but until I know that, I can't stop
-worrying.</t>
+          <t>I'm sure if we actually talked properly I'd think
+'oh, that's nothing,' but until I know that, I can't
+stop worrying.</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -4289,8 +4291,8 @@
       </c>
       <c r="B250" s="1" t="inlineStr">
         <is>
-          <t>Unable to read Rin-chan’s intentions, I rushed forward
-driven only by my panic.</t>
+          <t>Unable to read Rin-chan’s intentions, I rushed
+forward driven only by my panic.</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4521,9 +4523,9 @@
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t>I overreacted before I knew it, and Miru-chan recoiled
-with her whole body like a cat with its fur standing
-on end.</t>
+          <t>I overreacted before I knew it, and Miru-chan
+recoiled with her whole body like a cat with its fur
+standing on end.</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4720,8 +4722,8 @@
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t>Listening to Miru-chan, I twisted my neck as hard as I
-could.</t>
+          <t>Listening to Miru-chan, I twisted my neck as hard as
+I could.</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -5075,9 +5077,9 @@
       </c>
       <c r="B301" s="1" t="inlineStr">
         <is>
-          <t>「Yokai, you know, are always hanging around somewhere,
-and they're like ghosts that sometimes do naughty
-things, right？」</t>
+          <t>「Yokai, you know, are always hanging around
+somewhere, and they're like ghosts that sometimes do
+naughty things, right？」</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -5603,8 +5605,8 @@
       </c>
       <c r="B335" s="1" t="inlineStr">
         <is>
-          <t>「Oh！ The bell！ Come on, come on, everyone, please take
-your seats！」</t>
+          <t>「Oh！ The bell！ Come on, come on, everyone, please
+take your seats！」</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -6200,8 +6202,8 @@
       </c>
       <c r="B374" s="1" t="inlineStr">
         <is>
-          <t>When I let my shoulders drop a little, Rin-chan stared
-intently at my face.</t>
+          <t>When I let my shoulders drop a little, Rin-chan
+stared intently at my face.</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -6615,9 +6617,9 @@
       </c>
       <c r="B401" s="1" t="inlineStr">
         <is>
-          <t>「You won’t kiss me, you won’t take a bath with me… you
-don’t even want to have sex… I started wondering if
-you hate me now…」</t>
+          <t>「You won’t kiss me, you won’t take a bath with me…
+you don’t even want to have sex… I started wondering
+if you hate me now…」</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -6708,8 +6710,8 @@
       </c>
       <c r="B407" s="1" t="inlineStr">
         <is>
-          <t>Then, Rin-chan had an unexpectedly puzzled look on her
-face.</t>
+          <t>Then, Rin-chan had an unexpectedly puzzled look on
+her face.</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -6966,8 +6968,8 @@
       </c>
       <c r="B424" s="1" t="inlineStr">
         <is>
-          <t>I opened my mouth, and the whiskey bonbon Rin-chan was
-holding... with my lips...</t>
+          <t>I opened my mouth, and the whiskey bonbon Rin-chan
+was holding... with my lips...</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -7352,9 +7354,9 @@
       </c>
       <c r="B449" s="1" t="inlineStr">
         <is>
-          <t>Even though she'd eaten the whiskey bonbon, I couldn't
-handle the sudden change and just let Rin-chan do as
-she pleased.</t>
+          <t>Even though she'd eaten the whiskey bonbon, I
+couldn't handle the sudden change and just let
+Rin-chan do as she pleased.</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -7839,9 +7841,9 @@
       </c>
       <c r="B481" s="1" t="inlineStr">
         <is>
-          <t>And then she also pulled down her panties, exposed the
-area between her legs, grabbed the penis and pressed
-it against her crotch.</t>
+          <t>And then she also pulled down her panties, exposed
+the area between her legs, grabbed the penis and
+pressed it against her crotch.</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -8008,8 +8010,9 @@
       </c>
       <c r="B492" s="1" t="inlineStr">
         <is>
-          <t>It's because she's tipsy from whiskey bonbons, but the
-way she's drunk feels a little different from before.</t>
+          <t>It's because she's tipsy from whiskey bonbons, but
+the way she's drunk feels a little different from
+before.</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -8253,8 +8256,8 @@
       </c>
       <c r="B508" s="1" t="inlineStr">
         <is>
-          <t>「It's gotten so big... huh...！  Okay then... I'm gonna
-put it in, okay？」</t>
+          <t>「It's gotten so big... huh...！  Okay then... I'm
+gonna put it in, okay？」</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -8436,8 +8439,8 @@
       </c>
       <c r="B520" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan exhales hotly and reaches out with both hands
-to my cheek.</t>
+          <t>Rin-chan exhales hotly and reaches out with both
+hands to my cheek.</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -8818,8 +8821,8 @@
       </c>
       <c r="B545" s="1" t="inlineStr">
         <is>
-          <t>While I was spacing out, Rin-chan’s vagina had a penis
-fully buried inside it.</t>
+          <t>While I was spacing out, Rin-chan’s vagina had a
+penis fully buried inside it.</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -9034,8 +9037,8 @@
       </c>
       <c r="B559" s="1" t="inlineStr">
         <is>
-          <t>When I echoed her back, Rin-chan puffed out her cheeks
-and thrust her hips harder.</t>
+          <t>When I echoed her back, Rin-chan puffed out her
+cheeks and thrust her hips harder.</t>
         </is>
       </c>
       <c r="C559" t="n">
@@ -9356,8 +9359,8 @@
       </c>
       <c r="B580" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan likes me and she's having sex with me, so for
-now isn't that all that matters?</t>
+          <t>Rin-chan likes me and she's having sex with me, so
+for now isn't that all that matters?</t>
         </is>
       </c>
       <c r="C580" t="n">
@@ -9496,7 +9499,8 @@
       </c>
       <c r="B589" s="1" t="inlineStr">
         <is>
-          <t>…But now it doesn't seem like it's impossible anymore.</t>
+          <t>…But now it doesn't seem like it's impossible
+anymore.</t>
         </is>
       </c>
       <c r="C589" t="n">
@@ -9832,7 +9836,8 @@
       </c>
       <c r="B611" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan tries to compete with me by swaying her hips.</t>
+          <t>Rin-chan tries to compete with me by swaying her
+hips.</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -9986,8 +9991,8 @@
       </c>
       <c r="B621" s="1" t="inlineStr">
         <is>
-          <t>「Oh, really... then I'll make you cum, Rin-chan！ Hehe！
-Nn... nngh！」</t>
+          <t>「Oh, really... then I'll make you cum, Rin-chan！
+Hehe！ Nn... nngh！」</t>
         </is>
       </c>
       <c r="C621" t="n">
@@ -10142,8 +10147,8 @@
       </c>
       <c r="B631" s="1" t="inlineStr">
         <is>
-          <t>Every time Rin-chan shakes her hips, a squelch-squelch
-of lewd, wet noises echoes.</t>
+          <t>Every time Rin-chan shakes her hips, a
+squelch-squelch of lewd, wet noises echoes.</t>
         </is>
       </c>
       <c r="C631" t="n">
@@ -10507,8 +10512,8 @@
       </c>
       <c r="B655" s="1" t="inlineStr">
         <is>
-          <t>「…When you say that, it just makes me want to try even
-harder.」</t>
+          <t>「…When you say that, it just makes me want to try
+even harder.」</t>
         </is>
       </c>
       <c r="C655" t="n">
@@ -10585,9 +10590,9 @@
       </c>
       <c r="B660" s="1" t="inlineStr">
         <is>
-          <t>When the tip of my penis pressed against the depths of
-her vagina, Rin-chan opened her eyes wide and moaned
-with pleasure.</t>
+          <t>When the tip of my penis pressed against the depths
+of her vagina, Rin-chan opened her eyes wide and
+moaned with pleasure.</t>
         </is>
       </c>
       <c r="C660" t="n">
@@ -10770,8 +10775,8 @@
       </c>
       <c r="B672" s="1" t="inlineStr">
         <is>
-          <t>「Haa... ah... haaa！ Ya... Niini, shu-go...k, uu... fu,
-kuu...！」</t>
+          <t>「Haa... ah... haaa！ Ya... Niini, shu-go...k, uu...
+fu, kuu...！」</t>
         </is>
       </c>
       <c r="C672" t="n">
@@ -11167,8 +11172,8 @@
       <c r="B698" s="1" t="inlineStr">
         <is>
           <t>Being able to have sex without feeling
-self-conscious... just thinking that loosened the knot
-in my heart.</t>
+self-conscious... just thinking that loosened the
+knot in my heart.</t>
         </is>
       </c>
       <c r="C698" t="n">
@@ -11836,8 +11841,8 @@
       </c>
       <c r="B742" s="1" t="inlineStr">
         <is>
-          <t>Her tone was stubborn and determined, but I could tell
-she wanted to make me feel good.</t>
+          <t>Her tone was stubborn and determined, but I could
+tell she wanted to make me feel good.</t>
         </is>
       </c>
       <c r="C742" t="n">
@@ -12036,8 +12041,8 @@
       </c>
       <c r="B755" s="1" t="inlineStr">
         <is>
-          <t>「Noo—... not, not...！ I'm cumming... I'm gonna come...
-nngh！ Ah！ Hahhh...！」</t>
+          <t>「Noo—... not, not...！ I'm cumming... I'm gonna
+come... nngh！ Ah！ Hahhh...！」</t>
         </is>
       </c>
       <c r="C755" t="n">
@@ -12148,7 +12153,8 @@
       <c r="B762" s="1" t="inlineStr">
         <is>
           <t>When Rin-chan gets aroused, her love juices can't all
-stay inside her pussy and spill out from the junction.</t>
+stay inside her pussy and spill out from the
+junction.</t>
         </is>
       </c>
       <c r="C762" t="n">
@@ -12744,8 +12750,8 @@
       </c>
       <c r="B801" s="1" t="inlineStr">
         <is>
-          <t>As Rin-chan's vaginal muscles twitched, my cum spurted
-out too.</t>
+          <t>As Rin-chan's vaginal muscles twitched, my cum
+spurted out too.</t>
         </is>
       </c>
       <c r="C801" t="n">
@@ -13650,8 +13656,8 @@
       </c>
       <c r="B860" s="1" t="inlineStr">
         <is>
-          <t>From the way Nono-chan spoke earlier, I guess Rin-chan
-did write something but hasn't turned it in.</t>
+          <t>From the way Nono-chan spoke earlier, I guess
+Rin-chan did write something but hasn't turned it in.</t>
         </is>
       </c>
       <c r="C860" t="n">
@@ -14080,8 +14086,8 @@
       <c r="B888" s="1" t="inlineStr">
         <is>
           <t>Since I’m a direct line of Arisugawa, my path’s
-probably decided either way, but as long as the head’s
-still around they can do whatever they want.</t>
+probably decided either way, but as long as the
+head’s still around they can do whatever they want.</t>
         </is>
       </c>
       <c r="C888" t="n">
@@ -14220,8 +14226,8 @@
       </c>
       <c r="B897" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan was blushing, so Miru-chan clapped her hands
-loudly to hype things up.</t>
+          <t>Nono-chan was blushing, so Miru-chan clapped her
+hands loudly to hype things up.</t>
         </is>
       </c>
       <c r="C897" t="n">
@@ -14512,8 +14518,8 @@
       </c>
       <c r="B916" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan looked back at me with a face on the verge of
-tears.</t>
+          <t>Rin-chan looked back at me with a face on the verge
+of tears.</t>
         </is>
       </c>
       <c r="C916" t="n">
@@ -14759,8 +14765,8 @@
       </c>
       <c r="B932" s="1" t="inlineStr">
         <is>
-          <t>「I think I really have to clean properly... I want our
-home to be sparkling all the time, like Niini's.」</t>
+          <t>「I think I really have to clean properly... I want
+our home to be sparkling all the time, like Niini's.」</t>
         </is>
       </c>
       <c r="C932" t="n">
@@ -15005,8 +15011,8 @@
       </c>
       <c r="B948" s="1" t="inlineStr">
         <is>
-          <t>But with Rin-chan's personality, she probably couldn't
-bring herself to actually write it.</t>
+          <t>But with Rin-chan's personality, she probably
+couldn't bring herself to actually write it.</t>
         </is>
       </c>
       <c r="C948" t="n">
@@ -15021,8 +15027,8 @@
       </c>
       <c r="B949" s="1" t="inlineStr">
         <is>
-          <t>She got embarrassed by herself, banged her head on the
-desk... she was avoiding me because she was
+          <t>She got embarrassed by herself, banged her head on
+the desk... she was avoiding me because she was
 overthinking it and felt embarrassed.</t>
         </is>
       </c>

--- a/processed_ruby_restored_xlsx/sc239_凛Ｂ：ＥＮＤ.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc239_凛Ｂ：ＥＮＤ.ss.xlsx
@@ -652,8 +652,8 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>「You’re a kid because you don’t understand that, you
-know？」</t>
+          <t>You’re a kid because you don’t understand that, you
+know？</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>I mean, she's weirdly fidgety and can't sit still.</t>
+          <t>I mean, they're weirdly fidgety and can't sit still.</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ Janitor-sensei, you mustn't help, okay？」</t>
+          <t>Ah！ Janitor-sensei, you mustn't help, okay？</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -3032,8 +3032,8 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>「Janitor-sensei couldn't possibly write the whole
-thing, you know！」</t>
+          <t>Janitor-sensei couldn't possibly write the whole
+thing, you know！</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -4862,7 +4862,7 @@
       <c r="B287" s="1" t="inlineStr">
         <is>
           <t>After Miru-chan steered the conversation toward
-Rin-chan, my mind went there and I didn't notice
+Rin-chan, his mind went there and he didn't notice
 Rurichiyo-chan...</t>
         </is>
       </c>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>When I looked up, Nono-chan was on the other side.</t>
+          <t>When he looked up, Nono-chan was on the other side.</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="B368" s="1" t="inlineStr">
         <is>
-          <t>「C-Can I eat it...！？」</t>
+          <t>C-Can I eat it...！？</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t>「Y-yeah…」</t>
+          <t>Y-yeah…</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="B496" s="1" t="inlineStr">
         <is>
-          <t>「Nn... I don't knooow that stuff！」</t>
+          <t>Nn... I don't knooow that stuff！</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -8134,8 +8134,8 @@
       </c>
       <c r="B500" s="1" t="inlineStr">
         <is>
-          <t>「More importantly... can you make it really big for
-me...？」</t>
+          <t>More importantly... can you make it really big for
+me...？</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -8961,8 +8961,8 @@
       </c>
       <c r="B554" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ Nnn...！ Huh, nn...！ N'uh... Niini, does it feel
-good...？」</t>
+          <t>Nn！ Nnn...！ Huh, nn...！ N'uh... Niini, does it feel
+good...？</t>
         </is>
       </c>
       <c r="C554" t="n">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="B559" s="1" t="inlineStr">
         <is>
-          <t>When I echoed her back, Rin-chan puffed out her
+          <t>When he echoed her back, Rin-chan puffed out her
 cheeks and thrust her hips harder.</t>
         </is>
       </c>
@@ -9205,8 +9205,8 @@
       </c>
       <c r="B570" s="1" t="inlineStr">
         <is>
-          <t>I doesn't seem willing to say why I avoided me, but
-for now anyway, I want to tell me that I love me.</t>
+          <t>He doesn't seem willing to say why he avoided me, but
+for now anyway, he wants to tell me that he loves me.</t>
         </is>
       </c>
       <c r="C570" t="n">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="B586" s="1" t="inlineStr">
         <is>
-          <t>「Nyaaah—！ No—！ Niini, don't move— nn—, kuhhh—！」</t>
+          <t>Nyaaah—！ No—！ Niini, don't move— nn—, kuhhh—！</t>
         </is>
       </c>
       <c r="C586" t="n">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="B593" s="1" t="inlineStr">
         <is>
-          <t>「Nn—ah？　Eh？　Ah…！」</t>
+          <t>Nn—ah？　Eh？　Ah…！</t>
         </is>
       </c>
       <c r="C593" t="n">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="B595" s="1" t="inlineStr">
         <is>
-          <t>I thrust my hips up there once more...！</t>
+          <t>He thrust his hips up there once more...！</t>
         </is>
       </c>
       <c r="C595" t="n">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="B599" s="1" t="inlineStr">
         <is>
-          <t>「…huh…haa…！」</t>
+          <t>…huh…haa…！</t>
         </is>
       </c>
       <c r="C599" t="n">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="B603" s="1" t="inlineStr">
         <is>
-          <t>「Nyaa, Niini！ Nn... Niini！」</t>
+          <t>Nyaa, Niini！ Nn... Niini！</t>
         </is>
       </c>
       <c r="C603" t="n">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="B605" s="1" t="inlineStr">
         <is>
-          <t>「I love you, Rin-chan...！」</t>
+          <t>I love you, Rin-chan...！</t>
         </is>
       </c>
       <c r="C605" t="n">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="B615" s="1" t="inlineStr">
         <is>
-          <t>「Ahaha... so cute...」</t>
+          <t>Ahaha... so cute...</t>
         </is>
       </c>
       <c r="C615" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="B636" s="1" t="inlineStr">
         <is>
-          <t>「Nn, nnn~！ How's that？ Cumming, gonna cum？」</t>
+          <t>Nn, nnn~！ How's that？ Cumming, gonna cum？</t>
         </is>
       </c>
       <c r="C636" t="n">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="B641" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... this is payback！」</t>
+          <t>Ugh... this is payback！</t>
         </is>
       </c>
       <c r="C641" t="n">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="B643" s="1" t="inlineStr">
         <is>
-          <t>「U-ugh...！  Ya—ah！  Ah—no！」</t>
+          <t>U-ugh...！  Ya—ah！  Ah—no！</t>
         </is>
       </c>
       <c r="C643" t="n">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="B647" s="1" t="inlineStr">
         <is>
-          <t>「U, fuuuh！ Nn... nnn！ Nnah！ Yah... au, nn... nnn...！」</t>
+          <t>U, fuuuh！ Nn... nnn！ Nnah！ Yah... au, nn... nnn...！</t>
         </is>
       </c>
       <c r="C647" t="n">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="B657" s="1" t="inlineStr">
         <is>
-          <t>Then, holding Rin-chan in place, I thrust my hips
+          <t>Then, holding Rin-chan in place, he thrust his hips
 upward.</t>
         </is>
       </c>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="B660" s="1" t="inlineStr">
         <is>
-          <t>When the tip of my penis pressed against the depths
+          <t>When the tip of his penis pressed against the depths
 of her vagina, Rin-chan opened her eyes wide and
 moaned with pleasure.</t>
         </is>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="B670" s="1" t="inlineStr">
         <is>
-          <t>Somehow convinced, Hajime thrust my hips again, and
+          <t>Somehow convinced, Hajime thrust his hips again, and
 finally Rin-chan's breaths began to melt into moans.</t>
         </is>
       </c>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="B675" s="1" t="inlineStr">
         <is>
-          <t>With each swing of my hips, there were slurping,
+          <t>With each swing of his hips, there were slurping,
 slurping, lewd wet sounds.</t>
         </is>
       </c>
@@ -11079,7 +11079,7 @@
       </c>
       <c r="B692" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ Nnnh！ Nfuu, fuu, nnn...！」</t>
+          <t>Nn！ Nnnh！ Nfuu, fuu, nnn...！</t>
         </is>
       </c>
       <c r="C692" t="n">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="B695" s="1" t="inlineStr">
         <is>
-          <t>「Ah... aah... good, that's good...！」</t>
+          <t>Ah... aah... good, that's good...！</t>
         </is>
       </c>
       <c r="C695" t="n">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="B752" s="1" t="inlineStr">
         <is>
-          <t>Lift her into a half-squat and thrust up... rub the
+          <t>Lift them into a half-squat and thrust up... rub the
 tip’s hood against the narrow spot at the entrance of
 the vagina.</t>
         </is>
@@ -12057,7 +12057,7 @@
       </c>
       <c r="B756" s="1" t="inlineStr">
         <is>
-          <t>I dodged me earlier, but now I'm being oddly
+          <t>He dodged me earlier, but now he's being oddly
 straightforward...</t>
         </is>
       </c>
@@ -12136,8 +12136,8 @@
       </c>
       <c r="B761" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ Nn, nnn—！ Faa... ah！ Ah！ Unn... together,
-together...！」</t>
+          <t>Nn！ Nn, nnn—！ Faa... ah！ Ah！ Unn... together,
+together...！</t>
         </is>
       </c>
       <c r="C761" t="n">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="B789" s="1" t="inlineStr">
         <is>
-          <t>「'…Ahh！」</t>
+          <t>」…Ahh！</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="B792" s="1" t="inlineStr">
         <is>
-          <t>「Aaaahhhhhh！ Ah… nngaaah！ Haa…！ Haaahhh…！」</t>
+          <t>Aaaahhhhhh！ Ah… nngaaah！ Haa…！ Haaahhh…！</t>
         </is>
       </c>
       <c r="C792" t="n">
@@ -12874,8 +12874,8 @@
       <c r="B809" s="1" t="inlineStr">
         <is>
           <t>She’s been pushed to orgasm over and over, and at the
-exact same moment she’s got my cum on her stomach, so
-she looks like she can’t think about anything at
+exact same moment she’s got his cum on her stomach,
+so she looks like she can’t think about anything at
 all...</t>
         </is>
       </c>
@@ -13243,7 +13243,7 @@
       </c>
       <c r="B833" s="1" t="inlineStr">
         <is>
-          <t>「I like you more, Niini...！」</t>
+          <t>「I like you more, Nii-ni...！」</t>
         </is>
       </c>
       <c r="C833" t="n">
@@ -13333,7 +13333,7 @@
       </c>
       <c r="B839" s="1" t="inlineStr">
         <is>
-          <t>「Niini...」</t>
+          <t>「Nii-ni...」</t>
         </is>
       </c>
       <c r="C839" t="n">
@@ -15499,7 +15499,7 @@
       </c>
       <c r="B980" s="1" t="inlineStr">
         <is>
-          <t>「Geez... you always end up eating it, Rin-chan！」</t>
+          <t>Geez... you always end up eating it, Rin-chan！</t>
         </is>
       </c>
       <c r="C980" t="n">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="B982" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... I'm so happy...！」</t>
+          <t>Mmm... I'm so happy...！</t>
         </is>
       </c>
       <c r="C982" t="n">
